--- a/jaydeep.task1.xlsx
+++ b/jaydeep.task1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC6\Desktop\JAYDEEP.B.DA\Excel-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3487A38-C680-4F6C-B9C0-6E9FE4B8492A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E858C6F-8EE6-4FD2-B573-4C85E4B90725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{66CF3137-FEC5-46EC-ABF6-A8E9FEEFE1B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,121 +36,187 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
-  <si>
-    <t>Employee ID</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>Joining Date</t>
-  </si>
-  <si>
-    <t>E101</t>
-  </si>
-  <si>
-    <t>Amit Sharma</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="58">
   <si>
     <t>HR</t>
   </si>
   <si>
-    <t>E102</t>
-  </si>
-  <si>
-    <t>Neha Verma</t>
-  </si>
-  <si>
     <t>IT</t>
   </si>
   <si>
-    <t>E103</t>
-  </si>
-  <si>
-    <t>Rahul Mehta</t>
-  </si>
-  <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>18-07-2020</t>
-  </si>
-  <si>
-    <t>E104</t>
-  </si>
-  <si>
-    <t>Pooja Singh</t>
-  </si>
-  <si>
-    <t>E105</t>
-  </si>
-  <si>
-    <t>Ankit Patel</t>
-  </si>
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>25-06-2023</t>
-  </si>
-  <si>
-    <t>E106</t>
-  </si>
-  <si>
-    <t>E107</t>
-  </si>
-  <si>
-    <t>E108</t>
-  </si>
-  <si>
-    <t>E109</t>
-  </si>
-  <si>
-    <t>E110</t>
-  </si>
-  <si>
-    <t>E111</t>
-  </si>
-  <si>
-    <t>E112</t>
-  </si>
-  <si>
-    <t>E113</t>
-  </si>
-  <si>
-    <t>E114</t>
-  </si>
-  <si>
-    <t>E115</t>
-  </si>
-  <si>
-    <t>E116</t>
-  </si>
-  <si>
-    <t>E117</t>
-  </si>
-  <si>
-    <t>E118</t>
-  </si>
-  <si>
-    <t>E119</t>
-  </si>
-  <si>
-    <t>E120</t>
+    <t>EMP CODE</t>
+  </si>
+  <si>
+    <t>FIRST NAME</t>
+  </si>
+  <si>
+    <t>LAST NAME</t>
+  </si>
+  <si>
+    <t>SALARY</t>
+  </si>
+  <si>
+    <t>DEPARTMENT</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>EMP_101</t>
+  </si>
+  <si>
+    <t>RAMESH</t>
+  </si>
+  <si>
+    <t>KUMAR</t>
+  </si>
+  <si>
+    <t>EMP_102</t>
+  </si>
+  <si>
+    <t>EMP_103</t>
+  </si>
+  <si>
+    <t>EMP_104</t>
+  </si>
+  <si>
+    <t>EMP_105</t>
+  </si>
+  <si>
+    <t>EMP_106</t>
+  </si>
+  <si>
+    <t>EMP_107</t>
+  </si>
+  <si>
+    <t>EMP_108</t>
+  </si>
+  <si>
+    <t>EMP_109</t>
+  </si>
+  <si>
+    <t>EMP_110</t>
+  </si>
+  <si>
+    <t>EMP_111</t>
+  </si>
+  <si>
+    <t>EMP_112</t>
+  </si>
+  <si>
+    <t>EMP_113</t>
+  </si>
+  <si>
+    <t>EMP_114</t>
+  </si>
+  <si>
+    <t>EMP_115</t>
+  </si>
+  <si>
+    <t>EMP_116</t>
+  </si>
+  <si>
+    <t>EMP_117</t>
+  </si>
+  <si>
+    <t>EMP_118</t>
+  </si>
+  <si>
+    <t>EMP_119</t>
+  </si>
+  <si>
+    <t>EMP_120</t>
+  </si>
+  <si>
+    <t>JAYDEEP</t>
+  </si>
+  <si>
+    <t>YASH</t>
+  </si>
+  <si>
+    <t>NOMAN</t>
+  </si>
+  <si>
+    <t>DEV</t>
+  </si>
+  <si>
+    <t>KANIKA</t>
+  </si>
+  <si>
+    <t>ARTH</t>
+  </si>
+  <si>
+    <t>MEET</t>
+  </si>
+  <si>
+    <t>TUSHAR</t>
+  </si>
+  <si>
+    <t>VANSH</t>
+  </si>
+  <si>
+    <t>ADITYA</t>
+  </si>
+  <si>
+    <t>RAHUL</t>
+  </si>
+  <si>
+    <t>SAHIL</t>
+  </si>
+  <si>
+    <t>JINAL</t>
+  </si>
+  <si>
+    <t>EKTA</t>
+  </si>
+  <si>
+    <t>DHRUVI</t>
+  </si>
+  <si>
+    <t>OM</t>
+  </si>
+  <si>
+    <t>MAYUR</t>
+  </si>
+  <si>
+    <t>AMAN</t>
+  </si>
+  <si>
+    <t>SHAH</t>
+  </si>
+  <si>
+    <t>RAJPUT</t>
+  </si>
+  <si>
+    <t>SHARMA</t>
+  </si>
+  <si>
+    <t>JAIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   JAIN</t>
+  </si>
+  <si>
+    <t>FINANCE</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>MARKETING</t>
+  </si>
+  <si>
+    <t>EMP_123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,6 +238,21 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -205,43 +287,63 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFD1D9E0"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FFD1D9E0"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FFD1D9E0"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFD1D9E0"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -554,197 +656,942 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B16A2830-6B4F-4347-B123-30A84407AC2A}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="10">
+        <v>40000</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="str">
+        <f>_xlfn.CONCAT(LOWER(B2),RIGHT(A2,3),"@GMAIL.COM")</f>
+        <v>ramesh101@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="6">
+        <v>67447</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="str">
+        <f t="shared" ref="F3:F21" si="0">_xlfn.CONCAT(LOWER(B3),RIGHT(A3,3),"@GMAIL.COM")</f>
+        <v>jaydeep102@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="6">
+        <v>43434</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yash103@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="6">
+        <v>87358</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>noman104@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="6">
+        <v>66706</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>dev105@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="6">
+        <v>57735</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>kanika106@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="6">
+        <v>66498</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>arth107@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="6">
+        <v>53734</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>meet108@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="6">
+        <v>63736</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>tushar109@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="6">
+        <v>47061</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>vansh110@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6">
+        <v>63765</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>aditya111@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="6">
+        <v>73552</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>rahul112@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="6">
+        <v>84814</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>sahil113@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="6">
+        <v>40451</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>jinal114@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="6">
+        <v>58347</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>ekta115@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="6">
+        <v>50188</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>dhruvi116@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="6">
+        <v>55811</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>rahul117@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="6">
+        <v>87773</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>om118@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="6">
+        <v>49698</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2">
-        <v>32000</v>
-      </c>
-      <c r="E2" s="3">
-        <v>44896</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4">
-        <v>45000</v>
-      </c>
-      <c r="E3" s="5">
-        <v>44319</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2">
-        <v>38000</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="4">
-        <v>52000</v>
-      </c>
-      <c r="E5" s="5">
-        <v>43749</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2">
-        <v>30000</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="F20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>mayur119@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B21" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="6">
+        <v>58785</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>aman120@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{862F1495-B771-4390-94C1-6DBA02B6AEB0}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="10">
+        <v>40000</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="str">
+        <f>_xlfn.CONCAT(LOWER(B2),RIGHT(A2,3),"@GMAIL.COM")</f>
+        <v>ramesh101@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="6">
+        <v>67447</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="str">
+        <f t="shared" ref="F3:F21" si="0">_xlfn.CONCAT(LOWER(B3),RIGHT(A3,3),"@GMAIL.COM")</f>
+        <v>jaydeep102@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="6">
+        <v>43434</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yash103@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="6">
+        <v>87358</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>noman104@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="6">
+        <v>66706</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>dev105@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="6">
+        <v>57735</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>kanika106@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="6">
+        <v>66498</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>arth107@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="6">
+        <v>53734</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>meet108@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="6">
+        <v>63736</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>tushar109@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="6">
+        <v>47061</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>vansh110@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6">
+        <v>63765</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>aditya111@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="6">
+        <v>73552</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>rahul112@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="6">
+        <v>84814</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>sahil113@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="6">
+        <v>40451</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>jinal114@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="6">
+        <v>58347</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>ekta115@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="6">
+        <v>50188</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>dhruvi116@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="6">
+        <v>55811</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>rahul117@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="6">
+        <v>87773</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>om118@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="6">
+        <v>49698</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>mayur119@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="6">
+        <v>58785</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>aman120@GMAIL.COM</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="6">
+        <v>58785</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F22" t="str">
+        <f>CONCATENATE(LOWER(B22),RIGHT(A22,FIND("_",A22)))</f>
+        <v>aman_123</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>